--- a/Deliverables/SM_Top Board/_BOM/Client-BOM_Top_PCB_.xlsx
+++ b/Deliverables/SM_Top Board/_BOM/Client-BOM_Top_PCB_.xlsx
@@ -1,23 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303ECDFE-720C-43F4-9E0C-9825F0280B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SM_Top_PCB" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -809,9 +817,6 @@
     <t>OnlineComponents</t>
   </si>
   <si>
-    <t>Unable to find chinese supplier. Farnell has 11 parts in stock</t>
-  </si>
-  <si>
     <t>Custom</t>
   </si>
   <si>
@@ -1041,16 +1046,19 @@
   </si>
   <si>
     <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t>Custom Supplier</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.000"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.000"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -1572,7 +1580,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1584,10 +1592,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1626,12 +1634,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1644,15 +1652,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1680,13 +1679,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1710,40 +1709,40 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1752,7 +1751,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1765,7 +1764,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1789,7 +1788,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1807,13 +1806,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1844,7 +1843,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1871,7 +1870,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1895,10 +1894,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1911,22 +1910,49 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1935,24 +1961,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2235,7 +2243,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2261,42 +2269,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="129" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="30"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
+      <c r="M1" s="130"/>
+      <c r="N1" s="130"/>
+      <c r="O1" s="130"/>
+      <c r="P1" s="130"/>
+      <c r="Q1" s="130"/>
+      <c r="R1" s="130"/>
+      <c r="S1" s="131"/>
     </row>
     <row r="2" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="77" t="s">
         <v>174</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="77" t="s">
         <v>175</v>
       </c>
       <c r="F2" s="25" t="s">
@@ -2321,10 +2329,10 @@
         <v>179</v>
       </c>
       <c r="M2" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="N2" s="25" t="s">
         <v>266</v>
-      </c>
-      <c r="N2" s="25" t="s">
-        <v>267</v>
       </c>
       <c r="O2" s="25" t="s">
         <v>180</v>
@@ -2332,86 +2340,86 @@
       <c r="P2" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="Q2" s="85" t="s">
+      <c r="Q2" s="82" t="s">
+        <v>268</v>
+      </c>
+      <c r="R2" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="R2" s="25" t="s">
-        <v>270</v>
-      </c>
       <c r="S2" s="25" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24">
         <v>1</v>
       </c>
-      <c r="B3" s="126" t="s">
+      <c r="B3" s="132" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="86" t="s">
-        <v>263</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>279</v>
-      </c>
-      <c r="E3" s="32" t="s">
+      <c r="C3" s="83" t="s">
         <v>262</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="D3" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="F3" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="I3" s="46" t="s">
-        <v>271</v>
-      </c>
-      <c r="J3" s="59" t="s">
+      <c r="I3" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="J3" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="32">
+      <c r="K3" s="29">
         <v>25</v>
       </c>
-      <c r="L3" s="47">
+      <c r="L3" s="44">
         <v>1</v>
       </c>
-      <c r="M3" s="48">
+      <c r="M3" s="45">
         <f>L3*25</f>
         <v>25</v>
       </c>
-      <c r="N3" s="49" t="s">
+      <c r="N3" s="46" t="s">
         <v>216</v>
       </c>
-      <c r="O3" s="61">
+      <c r="O3" s="58">
         <v>0.24759999999999999</v>
       </c>
-      <c r="P3" s="51">
+      <c r="P3" s="48">
         <f>O3*L3</f>
         <v>0.24759999999999999</v>
       </c>
-      <c r="Q3" s="51">
+      <c r="Q3" s="48">
         <v>0.1915</v>
       </c>
-      <c r="R3" s="51">
+      <c r="R3" s="48">
         <f>Q3*K3</f>
         <v>4.7874999999999996</v>
       </c>
-      <c r="S3" s="62"/>
+      <c r="S3" s="59"/>
     </row>
     <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="24">
         <v>2</v>
       </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="87" t="s">
+      <c r="B4" s="133"/>
+      <c r="C4" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="31" t="s">
-        <v>280</v>
+      <c r="D4" s="28" t="s">
+        <v>279</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>7</v>
@@ -2426,7 +2434,7 @@
         <v>220</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J4" s="26" t="s">
         <v>5</v>
@@ -2458,23 +2466,23 @@
         <f>Q4*K4</f>
         <v>0.25</v>
       </c>
-      <c r="S4" s="71"/>
+      <c r="S4" s="68"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="24">
         <v>3</v>
       </c>
-      <c r="B5" s="127"/>
-      <c r="C5" s="87" t="s">
+      <c r="B5" s="133"/>
+      <c r="C5" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="28" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="66" t="s">
+      <c r="F5" s="63" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="6" t="s">
@@ -2516,21 +2524,21 @@
         <f t="shared" ref="R5:R21" si="1">Q5*K5</f>
         <v>2.6550000000000002</v>
       </c>
-      <c r="S5" s="71"/>
+      <c r="S5" s="68"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="24">
         <v>4</v>
       </c>
-      <c r="B6" s="127"/>
-      <c r="C6" s="87" t="s">
-        <v>264</v>
-      </c>
-      <c r="D6" s="31" t="s">
+      <c r="B6" s="133"/>
+      <c r="C6" s="84" t="s">
+        <v>263</v>
+      </c>
+      <c r="D6" s="28" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>16</v>
@@ -2542,7 +2550,7 @@
         <v>223</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J6" s="26" t="s">
         <v>14</v>
@@ -2574,21 +2582,21 @@
         <f t="shared" si="1"/>
         <v>7.9350000000000005</v>
       </c>
-      <c r="S6" s="71"/>
+      <c r="S6" s="68"/>
     </row>
     <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="24">
         <v>5</v>
       </c>
-      <c r="B7" s="127"/>
-      <c r="C7" s="87" t="s">
-        <v>265</v>
-      </c>
-      <c r="D7" s="31" t="s">
+      <c r="B7" s="133"/>
+      <c r="C7" s="84" t="s">
+        <v>264</v>
+      </c>
+      <c r="D7" s="28" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>19</v>
@@ -2600,7 +2608,7 @@
         <v>224</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J7" s="26" t="s">
         <v>17</v>
@@ -2632,17 +2640,17 @@
         <f t="shared" si="1"/>
         <v>2.375</v>
       </c>
-      <c r="S7" s="71"/>
+      <c r="S7" s="68"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="24">
         <v>6</v>
       </c>
-      <c r="B8" s="127"/>
-      <c r="C8" s="87" t="s">
+      <c r="B8" s="133"/>
+      <c r="C8" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="28" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -2658,7 +2666,7 @@
         <v>225</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J8" s="26" t="s">
         <v>20</v>
@@ -2690,17 +2698,17 @@
         <f t="shared" si="1"/>
         <v>0.21</v>
       </c>
-      <c r="S8" s="71"/>
+      <c r="S8" s="68"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24">
         <v>7</v>
       </c>
-      <c r="B9" s="127"/>
-      <c r="C9" s="87" t="s">
+      <c r="B9" s="133"/>
+      <c r="C9" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="28" t="s">
         <v>42</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -2716,7 +2724,7 @@
         <v>226</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J9" s="26" t="s">
         <v>24</v>
@@ -2748,33 +2756,33 @@
         <f t="shared" si="1"/>
         <v>1.3080000000000001</v>
       </c>
-      <c r="S9" s="71"/>
+      <c r="S9" s="68"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="24">
         <v>8</v>
       </c>
-      <c r="B10" s="127"/>
-      <c r="C10" s="87" t="s">
+      <c r="B10" s="133"/>
+      <c r="C10" s="84" t="s">
+        <v>281</v>
+      </c>
+      <c r="D10" s="28" t="s">
         <v>282</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="E10" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="F10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>285</v>
-      </c>
       <c r="H10" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J10" s="26" t="s">
         <v>3</v>
@@ -2806,36 +2814,36 @@
         <f t="shared" si="1"/>
         <v>8.07</v>
       </c>
-      <c r="S10" s="71"/>
+      <c r="S10" s="68"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="24">
         <v>9</v>
       </c>
-      <c r="B11" s="127"/>
-      <c r="C11" s="87" t="s">
+      <c r="B11" s="133"/>
+      <c r="C11" s="84" t="s">
+        <v>287</v>
+      </c>
+      <c r="D11" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="E11" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="G11" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>292</v>
-      </c>
       <c r="H11" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J11" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K11" s="6">
         <v>50</v>
@@ -2864,18 +2872,18 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="S11" s="71"/>
+      <c r="S11" s="68"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="24">
         <v>10</v>
       </c>
-      <c r="B12" s="127"/>
-      <c r="C12" s="87" t="s">
+      <c r="B12" s="133"/>
+      <c r="C12" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="31" t="s">
-        <v>281</v>
+      <c r="D12" s="28" t="s">
+        <v>280</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>26</v>
@@ -2890,7 +2898,7 @@
         <v>227</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J12" s="26" t="s">
         <v>28</v>
@@ -2912,7 +2920,7 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="P12" s="9">
-        <f>O12*K12</f>
+        <f t="shared" ref="P12:P19" si="2">O12*K12</f>
         <v>3.6700000000000004</v>
       </c>
       <c r="Q12" s="9">
@@ -2922,17 +2930,17 @@
         <f t="shared" si="1"/>
         <v>3.6700000000000004</v>
       </c>
-      <c r="S12" s="71"/>
+      <c r="S12" s="68"/>
     </row>
     <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="24">
         <v>11</v>
       </c>
-      <c r="B13" s="127"/>
-      <c r="C13" s="87" t="s">
+      <c r="B13" s="133"/>
+      <c r="C13" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -2948,7 +2956,7 @@
         <v>228</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J13" s="26" t="s">
         <v>31</v>
@@ -2970,7 +2978,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="P13" s="9">
-        <f>O13*K13</f>
+        <f t="shared" si="2"/>
         <v>1.38</v>
       </c>
       <c r="Q13" s="9">
@@ -2980,33 +2988,33 @@
         <f t="shared" si="1"/>
         <v>1.38</v>
       </c>
-      <c r="S13" s="71"/>
+      <c r="S13" s="68"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="24">
         <v>12</v>
       </c>
-      <c r="B14" s="127"/>
-      <c r="C14" s="87" t="s">
-        <v>286</v>
-      </c>
-      <c r="D14" s="31" t="s">
+      <c r="B14" s="133"/>
+      <c r="C14" s="84" t="s">
+        <v>285</v>
+      </c>
+      <c r="D14" s="28" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>5</v>
@@ -3028,7 +3036,7 @@
         <v>7.9000000000000008E-3</v>
       </c>
       <c r="P14" s="9">
-        <f>O14*K14</f>
+        <f t="shared" si="2"/>
         <v>0.39500000000000002</v>
       </c>
       <c r="Q14" s="9">
@@ -3038,23 +3046,23 @@
         <f t="shared" si="1"/>
         <v>0.39500000000000002</v>
       </c>
-      <c r="S14" s="71"/>
+      <c r="S14" s="68"/>
     </row>
     <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="24">
         <v>13</v>
       </c>
-      <c r="B15" s="127"/>
-      <c r="C15" s="87" t="s">
+      <c r="B15" s="133"/>
+      <c r="C15" s="84" t="s">
         <v>229</v>
       </c>
-      <c r="D15" s="131" t="s">
+      <c r="D15" s="123" t="s">
         <v>215</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="63" t="s">
         <v>230</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -3086,7 +3094,7 @@
         <v>1.9300000000000001E-2</v>
       </c>
       <c r="P15" s="9">
-        <f>O15*K15</f>
+        <f t="shared" si="2"/>
         <v>1.9300000000000002</v>
       </c>
       <c r="Q15" s="9">
@@ -3096,17 +3104,17 @@
         <f t="shared" si="1"/>
         <v>1.9300000000000002</v>
       </c>
-      <c r="S15" s="72"/>
+      <c r="S15" s="69"/>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="24">
         <v>14</v>
       </c>
-      <c r="B16" s="127"/>
-      <c r="C16" s="88" t="s">
+      <c r="B16" s="133"/>
+      <c r="C16" s="85" t="s">
         <v>211</v>
       </c>
-      <c r="D16" s="131" t="s">
+      <c r="D16" s="123" t="s">
         <v>212</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -3122,7 +3130,7 @@
         <v>231</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>36</v>
@@ -3144,7 +3152,7 @@
         <v>3.56E-2</v>
       </c>
       <c r="P16" s="9">
-        <f>O16*K16</f>
+        <f t="shared" si="2"/>
         <v>3.56</v>
       </c>
       <c r="Q16" s="9">
@@ -3154,33 +3162,33 @@
         <f t="shared" si="1"/>
         <v>3.56</v>
       </c>
-      <c r="S16" s="71"/>
+      <c r="S16" s="68"/>
     </row>
     <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="24">
         <v>15</v>
       </c>
-      <c r="B17" s="127"/>
-      <c r="C17" s="87" t="s">
+      <c r="B17" s="133"/>
+      <c r="C17" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="28" t="s">
         <v>39</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="66" t="s">
+      <c r="F17" s="63" t="s">
         <v>40</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>200</v>
       </c>
       <c r="H17" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="I17" s="14" t="s">
         <v>273</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>274</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>37</v>
@@ -3202,7 +3210,7 @@
         <v>5.1000000000000004E-3</v>
       </c>
       <c r="P17" s="9">
-        <f>O17*K17</f>
+        <f t="shared" si="2"/>
         <v>0.255</v>
       </c>
       <c r="Q17" s="9">
@@ -3212,17 +3220,17 @@
         <f t="shared" si="1"/>
         <v>0.255</v>
       </c>
-      <c r="S17" s="71"/>
+      <c r="S17" s="68"/>
     </row>
     <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="24">
         <v>16</v>
       </c>
-      <c r="B18" s="127"/>
-      <c r="C18" s="87" t="s">
+      <c r="B18" s="133"/>
+      <c r="C18" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="28" t="s">
         <v>42</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -3238,7 +3246,7 @@
         <v>226</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>41</v>
@@ -3260,7 +3268,7 @@
         <v>3.27E-2</v>
       </c>
       <c r="P18" s="9">
-        <f>O18*K18</f>
+        <f t="shared" si="2"/>
         <v>1.3080000000000001</v>
       </c>
       <c r="Q18" s="9">
@@ -3270,17 +3278,17 @@
         <f t="shared" si="1"/>
         <v>1.3080000000000001</v>
       </c>
-      <c r="S18" s="72"/>
+      <c r="S18" s="69"/>
     </row>
     <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="24">
         <v>17</v>
       </c>
-      <c r="B19" s="127"/>
-      <c r="C19" s="87" t="s">
+      <c r="B19" s="133"/>
+      <c r="C19" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="28" t="s">
         <v>45</v>
       </c>
       <c r="E19" s="6" t="s">
@@ -3296,7 +3304,7 @@
         <v>235</v>
       </c>
       <c r="I19" s="27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>43</v>
@@ -3318,7 +3326,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
       <c r="P19" s="9">
-        <f>O19*K19</f>
+        <f t="shared" si="2"/>
         <v>0.36</v>
       </c>
       <c r="Q19" s="9">
@@ -3328,96 +3336,96 @@
         <f t="shared" si="1"/>
         <v>0.36</v>
       </c>
-      <c r="S19" s="71"/>
+      <c r="S19" s="68"/>
     </row>
     <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="24">
         <v>18</v>
       </c>
-      <c r="B20" s="128"/>
-      <c r="C20" s="89" t="s">
+      <c r="B20" s="134"/>
+      <c r="C20" s="86" t="s">
+        <v>292</v>
+      </c>
+      <c r="D20" s="49" t="s">
         <v>293</v>
       </c>
-      <c r="D20" s="52" t="s">
+      <c r="E20" s="30" t="s">
         <v>294</v>
       </c>
-      <c r="E20" s="33" t="s">
+      <c r="F20" s="30" t="s">
         <v>295</v>
       </c>
-      <c r="F20" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="G20" s="33" t="s">
+      <c r="G20" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="H20" s="30" t="s">
         <v>318</v>
       </c>
-      <c r="H20" s="33" t="s">
+      <c r="I20" s="78" t="s">
+        <v>271</v>
+      </c>
+      <c r="J20" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="I20" s="81" t="s">
-        <v>272</v>
-      </c>
-      <c r="J20" s="33" t="s">
-        <v>320</v>
-      </c>
-      <c r="K20" s="33">
+      <c r="K20" s="30">
         <v>50</v>
       </c>
-      <c r="L20" s="53">
+      <c r="L20" s="50">
         <v>2</v>
       </c>
-      <c r="M20" s="82">
+      <c r="M20" s="79">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N20" s="54" t="s">
+      <c r="N20" s="51" t="s">
         <v>216</v>
       </c>
-      <c r="O20" s="83">
+      <c r="O20" s="80">
         <v>0.16539999999999999</v>
       </c>
-      <c r="P20" s="56">
+      <c r="P20" s="53">
         <f>O20*L20</f>
         <v>0.33079999999999998</v>
       </c>
-      <c r="Q20" s="56">
+      <c r="Q20" s="53">
         <v>0.1134</v>
       </c>
-      <c r="R20" s="56">
+      <c r="R20" s="53">
         <f t="shared" si="1"/>
         <v>5.67</v>
       </c>
-      <c r="S20" s="84"/>
+      <c r="S20" s="81"/>
     </row>
     <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="24">
         <v>19</v>
       </c>
-      <c r="B21" s="126" t="s">
+      <c r="B21" s="132" t="s">
         <v>183</v>
       </c>
-      <c r="C21" s="90" t="s">
+      <c r="C21" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="31" t="s">
         <v>50</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>48</v>
       </c>
       <c r="G21" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="I21" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="J21" s="17" t="s">
         <v>321</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="I21" s="44" t="s">
-        <v>271</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>322</v>
       </c>
       <c r="K21" s="17">
         <v>25</v>
@@ -3432,7 +3440,7 @@
       <c r="N21" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="O21" s="58">
+      <c r="O21" s="55">
         <v>0.25140000000000001</v>
       </c>
       <c r="P21" s="23">
@@ -3446,452 +3454,452 @@
         <f t="shared" si="1"/>
         <v>6.2850000000000001</v>
       </c>
-      <c r="S21" s="92"/>
+      <c r="S21" s="89"/>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="24">
         <v>20</v>
       </c>
-      <c r="B22" s="127"/>
-      <c r="C22" s="97" t="s">
+      <c r="B22" s="133"/>
+      <c r="C22" s="94" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="132" t="s">
+      <c r="D22" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="E22" s="98" t="s">
+      <c r="E22" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="98" t="s">
+      <c r="F22" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="G22" s="98" t="s">
-        <v>323</v>
-      </c>
-      <c r="H22" s="98" t="s">
-        <v>271</v>
-      </c>
-      <c r="I22" s="36" t="s">
-        <v>271</v>
-      </c>
-      <c r="J22" s="35" t="s">
+      <c r="G22" s="95" t="s">
         <v>322</v>
       </c>
-      <c r="K22" s="35">
+      <c r="H22" s="95" t="s">
+        <v>270</v>
+      </c>
+      <c r="I22" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="J22" s="32" t="s">
+        <v>321</v>
+      </c>
+      <c r="K22" s="32">
         <v>200</v>
       </c>
-      <c r="L22" s="37">
+      <c r="L22" s="34">
         <v>8</v>
       </c>
-      <c r="M22" s="43">
+      <c r="M22" s="40">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="N22" s="39" t="s">
+      <c r="N22" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="O22" s="96">
+      <c r="O22" s="93">
         <v>0.104</v>
       </c>
-      <c r="P22" s="41">
+      <c r="P22" s="38">
         <f>O22*10</f>
         <v>1.04</v>
       </c>
-      <c r="Q22" s="41">
+      <c r="Q22" s="38">
         <v>0.104</v>
       </c>
-      <c r="R22" s="41">
+      <c r="R22" s="38">
         <f>Q22*M22</f>
         <v>20.8</v>
       </c>
-      <c r="S22" s="99"/>
+      <c r="S22" s="96"/>
     </row>
     <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="24">
         <v>21</v>
       </c>
-      <c r="B23" s="126" t="s">
-        <v>298</v>
-      </c>
-      <c r="C23" s="86" t="s">
+      <c r="B23" s="132" t="s">
+        <v>297</v>
+      </c>
+      <c r="C23" s="83" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="45" t="s">
+      <c r="D23" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="E23" s="32" t="s">
-        <v>262</v>
-      </c>
-      <c r="F23" s="32" t="s">
+      <c r="E23" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="F23" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="G23" s="32" t="s">
+      <c r="G23" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="H23" s="32" t="s">
+      <c r="H23" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="I23" s="60" t="s">
+      <c r="I23" s="57" t="s">
+        <v>274</v>
+      </c>
+      <c r="J23" s="29" t="s">
         <v>275</v>
       </c>
-      <c r="J23" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="K23" s="32">
+      <c r="K23" s="29">
         <v>25</v>
       </c>
-      <c r="L23" s="47">
+      <c r="L23" s="44">
         <v>1</v>
       </c>
-      <c r="M23" s="48">
+      <c r="M23" s="45">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N23" s="49" t="s">
+      <c r="N23" s="46" t="s">
         <v>216</v>
       </c>
-      <c r="O23" s="61">
+      <c r="O23" s="58">
         <v>0.1181</v>
       </c>
-      <c r="P23" s="51">
+      <c r="P23" s="48">
         <f>O23*K23</f>
         <v>2.9525000000000001</v>
       </c>
-      <c r="Q23" s="51">
+      <c r="Q23" s="48">
         <v>0.1181</v>
       </c>
-      <c r="R23" s="51">
+      <c r="R23" s="48">
         <f>Q23*M23</f>
         <v>2.9525000000000001</v>
       </c>
-      <c r="S23" s="62"/>
+      <c r="S23" s="59"/>
     </row>
     <row r="24" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="24">
         <v>22</v>
       </c>
-      <c r="B24" s="128"/>
-      <c r="C24" s="89" t="s">
+      <c r="B24" s="134"/>
+      <c r="C24" s="86" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="52" t="s">
+      <c r="D24" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="E24" s="33" t="s">
+      <c r="E24" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="F24" s="67" t="s">
+      <c r="F24" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="G24" s="100" t="s">
-        <v>277</v>
-      </c>
-      <c r="H24" s="33" t="s">
+      <c r="G24" s="97" t="s">
+        <v>276</v>
+      </c>
+      <c r="H24" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="I24" s="33" t="s">
+      <c r="I24" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="J24" s="33" t="s">
-        <v>276</v>
-      </c>
-      <c r="K24" s="33">
+      <c r="J24" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="K24" s="30">
         <v>30</v>
       </c>
-      <c r="L24" s="53">
+      <c r="L24" s="50">
         <v>1</v>
       </c>
-      <c r="M24" s="82">
+      <c r="M24" s="79">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N24" s="54" t="s">
+      <c r="N24" s="51" t="s">
         <v>216</v>
       </c>
-      <c r="O24" s="55">
+      <c r="O24" s="52">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="P24" s="56">
+      <c r="P24" s="53">
         <f>O24*K24</f>
         <v>2.0100000000000002</v>
       </c>
-      <c r="Q24" s="56">
+      <c r="Q24" s="53">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="R24" s="56">
+      <c r="R24" s="53">
         <f>Q24*M24</f>
         <v>1.675</v>
       </c>
-      <c r="S24" s="57"/>
+      <c r="S24" s="54"/>
     </row>
     <row r="25" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="24">
         <v>23</v>
       </c>
-      <c r="B25" s="129" t="s">
+      <c r="B25" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="C25" s="101" t="s">
+      <c r="C25" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="133" t="s">
+      <c r="D25" s="125" t="s">
         <v>57</v>
       </c>
-      <c r="E25" s="102" t="s">
-        <v>262</v>
-      </c>
-      <c r="F25" s="102" t="s">
+      <c r="E25" s="99" t="s">
+        <v>261</v>
+      </c>
+      <c r="F25" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="G25" s="102" t="s">
+      <c r="G25" s="99" t="s">
         <v>206</v>
       </c>
-      <c r="H25" s="102" t="s">
+      <c r="H25" s="99" t="s">
         <v>242</v>
       </c>
-      <c r="I25" s="102" t="s">
-        <v>278</v>
-      </c>
-      <c r="J25" s="102" t="s">
-        <v>276</v>
-      </c>
-      <c r="K25" s="102">
+      <c r="I25" s="99" t="s">
+        <v>277</v>
+      </c>
+      <c r="J25" s="99" t="s">
+        <v>275</v>
+      </c>
+      <c r="K25" s="99">
         <v>25</v>
       </c>
-      <c r="L25" s="103">
+      <c r="L25" s="100">
         <v>1</v>
       </c>
-      <c r="M25" s="38">
+      <c r="M25" s="35">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N25" s="104" t="s">
+      <c r="N25" s="101" t="s">
         <v>234</v>
       </c>
-      <c r="O25" s="105">
+      <c r="O25" s="102">
         <v>0.1353</v>
       </c>
-      <c r="P25" s="42">
+      <c r="P25" s="39">
         <f>O25*L25</f>
         <v>0.1353</v>
       </c>
-      <c r="Q25" s="42">
+      <c r="Q25" s="39">
         <v>0.1353</v>
       </c>
-      <c r="R25" s="42">
+      <c r="R25" s="39">
         <f>Q25*M25</f>
         <v>3.3825000000000003</v>
       </c>
-      <c r="S25" s="106"/>
+      <c r="S25" s="103"/>
     </row>
     <row r="26" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="24">
         <v>24</v>
       </c>
-      <c r="B26" s="130" t="s">
+      <c r="B26" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="C26" s="107" t="s">
+      <c r="C26" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="D26" s="134" t="s">
+      <c r="D26" s="126" t="s">
         <v>72</v>
       </c>
-      <c r="E26" s="108" t="s">
-        <v>262</v>
-      </c>
-      <c r="F26" s="108" t="s">
+      <c r="E26" s="105" t="s">
+        <v>261</v>
+      </c>
+      <c r="F26" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="G26" s="109" t="s">
-        <v>324</v>
-      </c>
-      <c r="H26" s="108" t="s">
+      <c r="G26" s="106" t="s">
+        <v>323</v>
+      </c>
+      <c r="H26" s="105" t="s">
         <v>239</v>
       </c>
-      <c r="I26" s="108" t="s">
-        <v>278</v>
-      </c>
-      <c r="J26" s="108" t="s">
-        <v>276</v>
-      </c>
-      <c r="K26" s="108">
+      <c r="I26" s="105" t="s">
+        <v>277</v>
+      </c>
+      <c r="J26" s="105" t="s">
+        <v>275</v>
+      </c>
+      <c r="K26" s="105">
         <v>25</v>
       </c>
-      <c r="L26" s="110">
+      <c r="L26" s="107">
         <v>1</v>
       </c>
-      <c r="M26" s="111">
+      <c r="M26" s="108">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N26" s="112" t="s">
+      <c r="N26" s="109" t="s">
         <v>216</v>
       </c>
-      <c r="O26" s="113">
+      <c r="O26" s="110">
         <v>0.752</v>
       </c>
-      <c r="P26" s="114">
+      <c r="P26" s="111">
         <f>O26*L26</f>
         <v>0.752</v>
       </c>
-      <c r="Q26" s="114">
+      <c r="Q26" s="111">
         <v>0.752</v>
       </c>
-      <c r="R26" s="114">
+      <c r="R26" s="111">
         <f>Q26*M26</f>
         <v>18.8</v>
       </c>
-      <c r="S26" s="115"/>
+      <c r="S26" s="112"/>
     </row>
     <row r="27" spans="1:19" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="24">
         <v>25</v>
       </c>
-      <c r="B27" s="129" t="s">
+      <c r="B27" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="C27" s="101" t="s">
+      <c r="C27" s="98" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="133" t="s">
+      <c r="D27" s="125" t="s">
         <v>91</v>
       </c>
-      <c r="E27" s="102" t="s">
+      <c r="E27" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="F27" s="102" t="s">
+      <c r="F27" s="99" t="s">
         <v>89</v>
       </c>
-      <c r="G27" s="102" t="s">
-        <v>325</v>
-      </c>
-      <c r="H27" s="102" t="s">
+      <c r="G27" s="99" t="s">
+        <v>324</v>
+      </c>
+      <c r="H27" s="99" t="s">
         <v>240</v>
       </c>
-      <c r="I27" s="102" t="s">
-        <v>278</v>
-      </c>
-      <c r="J27" s="102" t="s">
-        <v>276</v>
-      </c>
-      <c r="K27" s="102">
+      <c r="I27" s="99" t="s">
+        <v>277</v>
+      </c>
+      <c r="J27" s="99" t="s">
+        <v>275</v>
+      </c>
+      <c r="K27" s="99">
         <v>200</v>
       </c>
-      <c r="L27" s="103">
+      <c r="L27" s="100">
         <v>8</v>
       </c>
-      <c r="M27" s="38">
+      <c r="M27" s="35">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="N27" s="104" t="s">
+      <c r="N27" s="101" t="s">
         <v>234</v>
       </c>
-      <c r="O27" s="105">
+      <c r="O27" s="102">
         <v>0.72240000000000004</v>
       </c>
-      <c r="P27" s="42">
+      <c r="P27" s="39">
         <f>O27*L27</f>
         <v>5.7792000000000003</v>
       </c>
-      <c r="Q27" s="42">
+      <c r="Q27" s="39">
         <v>0.72240000000000004</v>
       </c>
-      <c r="R27" s="42">
+      <c r="R27" s="39">
         <f>Q27*K27</f>
         <v>144.48000000000002</v>
       </c>
-      <c r="S27" s="106"/>
+      <c r="S27" s="103"/>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="24">
         <v>26</v>
       </c>
-      <c r="B28" s="126" t="s">
+      <c r="B28" s="132" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="86" t="s">
+      <c r="C28" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="45" t="s">
+      <c r="D28" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="E28" s="32" t="s">
+      <c r="E28" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="32" t="s">
+      <c r="F28" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="G28" s="32" t="s">
+      <c r="G28" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="H28" s="32" t="s">
+      <c r="H28" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="I28" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="J28" s="32" t="s">
+      <c r="I28" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="J28" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="29">
         <v>100</v>
       </c>
-      <c r="L28" s="47">
+      <c r="L28" s="44">
         <v>2</v>
       </c>
-      <c r="M28" s="48">
+      <c r="M28" s="45">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N28" s="49" t="s">
+      <c r="N28" s="46" t="s">
         <v>216</v>
       </c>
-      <c r="O28" s="50">
+      <c r="O28" s="47">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="P28" s="51">
-        <f>O28*K28</f>
+      <c r="P28" s="48">
+        <f t="shared" ref="P28:P41" si="3">O28*K28</f>
         <v>0.11</v>
       </c>
-      <c r="Q28" s="51">
+      <c r="Q28" s="48">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="R28" s="51">
-        <f t="shared" ref="R28:R56" si="2">Q28*K28</f>
+      <c r="R28" s="48">
+        <f t="shared" ref="R28:R56" si="4">Q28*K28</f>
         <v>0.11</v>
       </c>
-      <c r="S28" s="62"/>
+      <c r="S28" s="59"/>
     </row>
-    <row r="29" spans="1:19" s="65" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" s="62" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="24">
         <v>27</v>
       </c>
-      <c r="B29" s="127"/>
-      <c r="C29" s="87" t="s">
-        <v>299</v>
-      </c>
-      <c r="D29" s="31" t="s">
+      <c r="B29" s="133"/>
+      <c r="C29" s="84" t="s">
+        <v>298</v>
+      </c>
+      <c r="D29" s="28" t="s">
         <v>97</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>46</v>
       </c>
       <c r="F29" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="G29" s="6" t="s">
-        <v>301</v>
-      </c>
       <c r="H29" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K29" s="2">
         <v>40</v>
@@ -3903,34 +3911,34 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N29" s="63" t="s">
+      <c r="N29" s="60" t="s">
         <v>216</v>
       </c>
       <c r="O29" s="4">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="P29" s="64">
-        <f>O29*K29</f>
+      <c r="P29" s="61">
+        <f t="shared" si="3"/>
         <v>0.72</v>
       </c>
-      <c r="Q29" s="64">
+      <c r="Q29" s="61">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.72</v>
       </c>
-      <c r="S29" s="74"/>
+      <c r="S29" s="71"/>
     </row>
     <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="24">
         <v>28</v>
       </c>
-      <c r="B30" s="127"/>
-      <c r="C30" s="87" t="s">
+      <c r="B30" s="133"/>
+      <c r="C30" s="84" t="s">
         <v>99</v>
       </c>
-      <c r="D30" s="31" t="s">
+      <c r="D30" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="6" t="s">
@@ -3946,7 +3954,7 @@
         <v>243</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>98</v>
@@ -3968,27 +3976,27 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="P30" s="9">
-        <f>O30*K30</f>
+        <f t="shared" si="3"/>
         <v>0.12</v>
       </c>
       <c r="Q30" s="9">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.12</v>
       </c>
-      <c r="S30" s="71"/>
+      <c r="S30" s="68"/>
     </row>
     <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="24">
         <v>29</v>
       </c>
-      <c r="B31" s="127"/>
-      <c r="C31" s="87" t="s">
+      <c r="B31" s="133"/>
+      <c r="C31" s="84" t="s">
         <v>103</v>
       </c>
-      <c r="D31" s="31" t="s">
+      <c r="D31" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E31" s="6" t="s">
@@ -4004,7 +4012,7 @@
         <v>244</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>102</v>
@@ -4026,27 +4034,27 @@
         <v>1.4E-3</v>
       </c>
       <c r="P31" s="9">
-        <f>O31*K31</f>
+        <f t="shared" si="3"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="Q31" s="9">
         <v>1.4E-3</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="S31" s="71"/>
+      <c r="S31" s="68"/>
     </row>
     <row r="32" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="24">
         <v>30</v>
       </c>
-      <c r="B32" s="127"/>
-      <c r="C32" s="87" t="s">
-        <v>302</v>
-      </c>
-      <c r="D32" s="31" t="s">
+      <c r="B32" s="133"/>
+      <c r="C32" s="84" t="s">
+        <v>301</v>
+      </c>
+      <c r="D32" s="28" t="s">
         <v>107</v>
       </c>
       <c r="E32" s="6" t="s">
@@ -4059,10 +4067,10 @@
         <v>191</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>106</v>
@@ -4078,33 +4086,33 @@
         <v>100</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O32" s="8">
         <v>0.1</v>
       </c>
       <c r="P32" s="9">
-        <f>O32*K32</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="Q32" s="9">
         <v>0.1</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="S32" s="71"/>
+      <c r="S32" s="68"/>
     </row>
     <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="24">
         <v>31</v>
       </c>
-      <c r="B33" s="127"/>
-      <c r="C33" s="87" t="s">
+      <c r="B33" s="133"/>
+      <c r="C33" s="84" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="31" t="s">
+      <c r="D33" s="28" t="s">
         <v>112</v>
       </c>
       <c r="E33" s="6" t="s">
@@ -4120,7 +4128,7 @@
         <v>245</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>110</v>
@@ -4135,34 +4143,34 @@
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="N33" s="63" t="s">
+      <c r="N33" s="60" t="s">
         <v>216</v>
       </c>
       <c r="O33" s="8">
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="P33" s="9">
-        <f>O33*K33</f>
+        <f t="shared" si="3"/>
         <v>0.33999999999999997</v>
       </c>
       <c r="Q33" s="9">
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.33999999999999997</v>
       </c>
-      <c r="S33" s="71"/>
+      <c r="S33" s="68"/>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="24">
         <v>32</v>
       </c>
-      <c r="B34" s="127"/>
-      <c r="C34" s="87" t="s">
+      <c r="B34" s="133"/>
+      <c r="C34" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="D34" s="31" t="s">
+      <c r="D34" s="28" t="s">
         <v>116</v>
       </c>
       <c r="E34" s="6" t="s">
@@ -4172,13 +4180,13 @@
         <v>117</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>246</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>114</v>
@@ -4200,27 +4208,27 @@
         <v>8.3999999999999995E-3</v>
       </c>
       <c r="P34" s="9">
-        <f>O34*K34</f>
+        <f t="shared" si="3"/>
         <v>0.42</v>
       </c>
       <c r="Q34" s="9">
         <v>8.3999999999999995E-3</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.42</v>
       </c>
-      <c r="S34" s="71"/>
+      <c r="S34" s="68"/>
     </row>
     <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="24">
         <v>33</v>
       </c>
-      <c r="B35" s="127"/>
-      <c r="C35" s="87" t="s">
+      <c r="B35" s="133"/>
+      <c r="C35" s="84" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="31" t="s">
+      <c r="D35" s="28" t="s">
         <v>120</v>
       </c>
       <c r="E35" s="6" t="s">
@@ -4236,7 +4244,7 @@
         <v>247</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>118</v>
@@ -4258,27 +4266,27 @@
         <v>1.5E-3</v>
       </c>
       <c r="P35" s="9">
-        <f>O35*K35</f>
+        <f t="shared" si="3"/>
         <v>0.15</v>
       </c>
       <c r="Q35" s="9">
         <v>1.5E-3</v>
       </c>
       <c r="R35" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.15</v>
       </c>
-      <c r="S35" s="71"/>
+      <c r="S35" s="68"/>
     </row>
     <row r="36" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="24">
         <v>34</v>
       </c>
-      <c r="B36" s="127"/>
-      <c r="C36" s="87" t="s">
+      <c r="B36" s="133"/>
+      <c r="C36" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="31" t="s">
+      <c r="D36" s="28" t="s">
         <v>124</v>
       </c>
       <c r="E36" s="6" t="s">
@@ -4288,13 +4296,13 @@
         <v>125</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>122</v>
@@ -4316,27 +4324,27 @@
         <v>1.4E-2</v>
       </c>
       <c r="P36" s="9">
-        <f>O36*K36</f>
+        <f t="shared" si="3"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="Q36" s="9">
         <v>1.4E-2</v>
       </c>
       <c r="R36" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="S36" s="71"/>
+      <c r="S36" s="68"/>
     </row>
     <row r="37" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="24">
         <v>35</v>
       </c>
-      <c r="B37" s="127"/>
-      <c r="C37" s="87" t="s">
+      <c r="B37" s="133"/>
+      <c r="C37" s="84" t="s">
         <v>127</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="D37" s="28" t="s">
         <v>128</v>
       </c>
       <c r="E37" s="6" t="s">
@@ -4352,7 +4360,7 @@
         <v>248</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>126</v>
@@ -4374,27 +4382,27 @@
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="P37" s="9">
-        <f>O37*K37</f>
+        <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
       <c r="Q37" s="9">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="R37" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.13</v>
       </c>
-      <c r="S37" s="71"/>
+      <c r="S37" s="68"/>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="24">
         <v>36</v>
       </c>
-      <c r="B38" s="127"/>
-      <c r="C38" s="87" t="s">
+      <c r="B38" s="133"/>
+      <c r="C38" s="84" t="s">
         <v>131</v>
       </c>
-      <c r="D38" s="31" t="s">
+      <c r="D38" s="28" t="s">
         <v>132</v>
       </c>
       <c r="E38" s="6" t="s">
@@ -4404,13 +4412,13 @@
         <v>133</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>249</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>130</v>
@@ -4432,27 +4440,27 @@
         <v>8.6E-3</v>
       </c>
       <c r="P38" s="9">
-        <f>O38*K38</f>
+        <f t="shared" si="3"/>
         <v>0.43</v>
       </c>
       <c r="Q38" s="9">
         <v>8.6E-3</v>
       </c>
       <c r="R38" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.43</v>
       </c>
-      <c r="S38" s="71"/>
+      <c r="S38" s="68"/>
     </row>
     <row r="39" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="24">
         <v>37</v>
       </c>
-      <c r="B39" s="127"/>
-      <c r="C39" s="87" t="s">
+      <c r="B39" s="133"/>
+      <c r="C39" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="D39" s="31" t="s">
+      <c r="D39" s="28" t="s">
         <v>136</v>
       </c>
       <c r="E39" s="6" t="s">
@@ -4468,7 +4476,7 @@
         <v>250</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J39" s="6" t="s">
         <v>134</v>
@@ -4490,27 +4498,27 @@
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="P39" s="9">
-        <f>O39*K39</f>
+        <f t="shared" si="3"/>
         <v>0.22</v>
       </c>
       <c r="Q39" s="9">
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="R39" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.22</v>
       </c>
-      <c r="S39" s="71"/>
+      <c r="S39" s="68"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="24">
         <v>38</v>
       </c>
-      <c r="B40" s="127"/>
-      <c r="C40" s="87" t="s">
+      <c r="B40" s="133"/>
+      <c r="C40" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="D40" s="31" t="s">
+      <c r="D40" s="28" t="s">
         <v>140</v>
       </c>
       <c r="E40" s="6" t="s">
@@ -4526,7 +4534,7 @@
         <v>251</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>138</v>
@@ -4548,106 +4556,106 @@
         <v>1.6000000000000001E-3</v>
       </c>
       <c r="P40" s="9">
-        <f>O40*K40</f>
+        <f t="shared" si="3"/>
         <v>0.16</v>
       </c>
       <c r="Q40" s="9">
         <v>1.6000000000000001E-3</v>
       </c>
       <c r="R40" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.16</v>
       </c>
-      <c r="S40" s="71"/>
+      <c r="S40" s="68"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="24">
         <v>39</v>
       </c>
-      <c r="B41" s="128"/>
-      <c r="C41" s="89" t="s">
+      <c r="B41" s="134"/>
+      <c r="C41" s="86" t="s">
+        <v>303</v>
+      </c>
+      <c r="D41" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="D41" s="52" t="s">
+      <c r="E41" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="E41" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="F41" s="33" t="s">
-        <v>306</v>
-      </c>
-      <c r="G41" s="33" t="s">
+      <c r="G41" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="H41" s="33" t="s">
-        <v>327</v>
-      </c>
-      <c r="I41" s="33" t="s">
-        <v>271</v>
-      </c>
-      <c r="J41" s="33" t="s">
-        <v>308</v>
-      </c>
-      <c r="K41" s="33">
+      <c r="H41" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="I41" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="J41" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="K41" s="30">
         <v>100</v>
       </c>
-      <c r="L41" s="53">
+      <c r="L41" s="50">
         <v>4</v>
       </c>
-      <c r="M41" s="82">
+      <c r="M41" s="79">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="N41" s="54" t="s">
+      <c r="N41" s="51" t="s">
         <v>216</v>
       </c>
-      <c r="O41" s="83">
+      <c r="O41" s="80">
         <v>1E-3</v>
       </c>
-      <c r="P41" s="56">
-        <f>O41*K41</f>
+      <c r="P41" s="53">
+        <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
-      <c r="Q41" s="56">
+      <c r="Q41" s="53">
         <v>1E-3</v>
       </c>
-      <c r="R41" s="56">
-        <f t="shared" si="2"/>
+      <c r="R41" s="53">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="S41" s="84"/>
+      <c r="S41" s="81"/>
     </row>
     <row r="42" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="24">
         <v>40</v>
       </c>
-      <c r="B42" s="127" t="s">
+      <c r="B42" s="133" t="s">
         <v>188</v>
       </c>
-      <c r="C42" s="90" t="s">
+      <c r="C42" s="87" t="s">
         <v>145</v>
       </c>
-      <c r="D42" s="34" t="s">
+      <c r="D42" s="31" t="s">
         <v>146</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>144</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K42" s="17">
         <v>50</v>
@@ -4666,7 +4674,7 @@
         <v>2.5499999999999998</v>
       </c>
       <c r="P42" s="23">
-        <f>O42*L42</f>
+        <f t="shared" ref="P42:P53" si="5">O42*L42</f>
         <v>2.5499999999999998</v>
       </c>
       <c r="Q42" s="23">
@@ -4675,135 +4683,135 @@
       <c r="R42" s="23">
         <v>2.5499999999999998</v>
       </c>
-      <c r="S42" s="70"/>
+      <c r="S42" s="67"/>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="24">
         <v>41</v>
       </c>
-      <c r="B43" s="127"/>
-      <c r="C43" s="95" t="s">
+      <c r="B43" s="133"/>
+      <c r="C43" s="92" t="s">
         <v>148</v>
       </c>
-      <c r="D43" s="132" t="s">
+      <c r="D43" s="124" t="s">
         <v>149</v>
       </c>
-      <c r="E43" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="F43" s="35" t="s">
+      <c r="E43" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="F43" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="G43" s="43" t="s">
+      <c r="G43" s="40" t="s">
         <v>253</v>
       </c>
-      <c r="H43" s="43" t="s">
+      <c r="H43" s="40" t="s">
         <v>252</v>
       </c>
-      <c r="I43" s="35" t="s">
-        <v>271</v>
-      </c>
-      <c r="J43" s="35" t="s">
-        <v>271</v>
-      </c>
-      <c r="K43" s="35">
+      <c r="I43" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="J43" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="K43" s="32">
         <v>50</v>
       </c>
-      <c r="L43" s="37">
+      <c r="L43" s="34">
         <v>2</v>
       </c>
-      <c r="M43" s="43">
+      <c r="M43" s="40">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N43" s="39" t="s">
+      <c r="N43" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="O43" s="40">
+      <c r="O43" s="37">
         <v>0.28449999999999998</v>
       </c>
-      <c r="P43" s="41">
-        <f>O43*L43</f>
+      <c r="P43" s="38">
+        <f t="shared" si="5"/>
         <v>0.56899999999999995</v>
       </c>
-      <c r="Q43" s="41">
+      <c r="Q43" s="38">
         <v>0.19070000000000001</v>
       </c>
-      <c r="R43" s="41">
-        <f t="shared" si="2"/>
+      <c r="R43" s="38">
+        <f t="shared" si="4"/>
         <v>9.5350000000000001</v>
       </c>
-      <c r="S43" s="73"/>
+      <c r="S43" s="70"/>
     </row>
     <row r="44" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="24">
         <v>42</v>
       </c>
-      <c r="B44" s="126" t="s">
+      <c r="B44" s="132" t="s">
         <v>189</v>
       </c>
-      <c r="C44" s="86" t="s">
+      <c r="C44" s="83" t="s">
         <v>151</v>
       </c>
-      <c r="D44" s="45" t="s">
+      <c r="D44" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="E44" s="32" t="s">
+      <c r="E44" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="F44" s="32" t="s">
+      <c r="F44" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="G44" s="48" t="s">
+      <c r="G44" s="45" t="s">
         <v>194</v>
       </c>
-      <c r="H44" s="48" t="s">
+      <c r="H44" s="45" t="s">
         <v>254</v>
       </c>
-      <c r="I44" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="J44" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="K44" s="32">
+      <c r="I44" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="J44" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="K44" s="29">
         <v>25</v>
       </c>
-      <c r="L44" s="47">
+      <c r="L44" s="44">
         <v>1</v>
       </c>
-      <c r="M44" s="48">
+      <c r="M44" s="45">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N44" s="49" t="s">
+      <c r="N44" s="46" t="s">
         <v>216</v>
       </c>
-      <c r="O44" s="61">
+      <c r="O44" s="58">
         <v>0.20369999999999999</v>
       </c>
-      <c r="P44" s="51">
-        <f>O44*L44</f>
+      <c r="P44" s="48">
+        <f t="shared" si="5"/>
         <v>0.20369999999999999</v>
       </c>
-      <c r="Q44" s="51">
+      <c r="Q44" s="48">
         <v>0.20369999999999999</v>
       </c>
-      <c r="R44" s="51">
-        <f t="shared" si="2"/>
+      <c r="R44" s="48">
+        <f t="shared" si="4"/>
         <v>5.0924999999999994</v>
       </c>
-      <c r="S44" s="117"/>
+      <c r="S44" s="114"/>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="24">
         <v>43</v>
       </c>
-      <c r="B45" s="127"/>
-      <c r="C45" s="87" t="s">
+      <c r="B45" s="133"/>
+      <c r="C45" s="84" t="s">
         <v>155</v>
       </c>
-      <c r="D45" s="31" t="s">
+      <c r="D45" s="28" t="s">
         <v>156</v>
       </c>
       <c r="E45" s="6" t="s">
@@ -4819,10 +4827,10 @@
         <v>256</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K45" s="6">
         <v>25</v>
@@ -4841,46 +4849,46 @@
         <v>0.32929999999999998</v>
       </c>
       <c r="P45" s="9">
-        <f>O45*L45</f>
+        <f t="shared" si="5"/>
         <v>0.32929999999999998</v>
       </c>
       <c r="Q45" s="9">
         <v>0.32929999999999998</v>
       </c>
       <c r="R45" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.2324999999999999</v>
       </c>
-      <c r="S45" s="71"/>
+      <c r="S45" s="68"/>
     </row>
     <row r="46" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="24">
         <v>44</v>
       </c>
-      <c r="B46" s="127"/>
-      <c r="C46" s="87" t="s">
+      <c r="B46" s="133"/>
+      <c r="C46" s="84" t="s">
+        <v>308</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="D46" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="E46" s="6" t="s">
+      <c r="F46" s="6" t="s">
         <v>310</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>311</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>195</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K46" s="6">
         <v>25</v>
@@ -4899,46 +4907,46 @@
         <v>0.39750000000000002</v>
       </c>
       <c r="P46" s="9">
-        <f>O46*L46</f>
+        <f t="shared" si="5"/>
         <v>0.39750000000000002</v>
       </c>
       <c r="Q46" s="9">
         <v>0.39750000000000002</v>
       </c>
       <c r="R46" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.9375</v>
       </c>
-      <c r="S46" s="71"/>
+      <c r="S46" s="68"/>
     </row>
     <row r="47" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="24">
         <v>45</v>
       </c>
-      <c r="B47" s="127"/>
-      <c r="C47" s="87" t="s">
-        <v>313</v>
-      </c>
-      <c r="D47" s="31" t="s">
+      <c r="B47" s="133"/>
+      <c r="C47" s="84" t="s">
+        <v>312</v>
+      </c>
+      <c r="D47" s="28" t="s">
         <v>159</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G47" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="H47" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="H47" s="5" t="s">
-        <v>330</v>
-      </c>
       <c r="I47" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K47" s="6">
         <v>25</v>
@@ -4957,27 +4965,27 @@
         <v>0.50860000000000005</v>
       </c>
       <c r="P47" s="9">
-        <f>O47*L47</f>
+        <f t="shared" si="5"/>
         <v>0.50860000000000005</v>
       </c>
       <c r="Q47" s="9">
         <v>0.40760000000000002</v>
       </c>
       <c r="R47" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>10.190000000000001</v>
       </c>
-      <c r="S47" s="71"/>
+      <c r="S47" s="68"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="24">
         <v>46</v>
       </c>
-      <c r="B48" s="127"/>
-      <c r="C48" s="87" t="s">
+      <c r="B48" s="133"/>
+      <c r="C48" s="84" t="s">
         <v>161</v>
       </c>
-      <c r="D48" s="31" t="s">
+      <c r="D48" s="28" t="s">
         <v>162</v>
       </c>
       <c r="E48" s="6" t="s">
@@ -4989,14 +4997,14 @@
       <c r="G48" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="H48" s="68" t="s">
-        <v>272</v>
+      <c r="H48" s="65" t="s">
+        <v>271</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K48" s="6">
         <v>25</v>
@@ -5015,27 +5023,27 @@
         <v>0.16039999999999999</v>
       </c>
       <c r="P48" s="9">
-        <f>O48*L48</f>
+        <f t="shared" si="5"/>
         <v>0.16039999999999999</v>
       </c>
       <c r="Q48" s="9">
         <v>0.16039999999999999</v>
       </c>
       <c r="R48" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.01</v>
       </c>
-      <c r="S48" s="71"/>
+      <c r="S48" s="68"/>
     </row>
     <row r="49" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="24">
         <v>47</v>
       </c>
-      <c r="B49" s="127"/>
-      <c r="C49" s="87" t="s">
+      <c r="B49" s="133"/>
+      <c r="C49" s="84" t="s">
         <v>165</v>
       </c>
-      <c r="D49" s="31" t="s">
+      <c r="D49" s="28" t="s">
         <v>166</v>
       </c>
       <c r="E49" s="6" t="s">
@@ -5045,16 +5053,16 @@
         <v>164</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="H49" s="68" t="s">
-        <v>272</v>
-      </c>
-      <c r="I49" s="68" t="s">
+        <v>330</v>
+      </c>
+      <c r="H49" s="65" t="s">
         <v>271</v>
       </c>
+      <c r="I49" s="65" t="s">
+        <v>270</v>
+      </c>
       <c r="J49" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K49" s="6">
         <v>30</v>
@@ -5073,7 +5081,7 @@
         <v>7.03</v>
       </c>
       <c r="P49" s="9">
-        <f>O49*L49</f>
+        <f t="shared" si="5"/>
         <v>7.03</v>
       </c>
       <c r="Q49" s="9">
@@ -5083,81 +5091,81 @@
         <f>Q49*K49</f>
         <v>210.9</v>
       </c>
-      <c r="S49" s="71"/>
+      <c r="S49" s="68"/>
     </row>
     <row r="50" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="24">
         <v>48</v>
       </c>
-      <c r="B50" s="128"/>
-      <c r="C50" s="89" t="s">
+      <c r="B50" s="134"/>
+      <c r="C50" s="86" t="s">
         <v>169</v>
       </c>
-      <c r="D50" s="52" t="s">
+      <c r="D50" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="E50" s="33" t="s">
+      <c r="E50" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="F50" s="33" t="s">
+      <c r="F50" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="G50" s="82" t="s">
+      <c r="G50" s="79" t="s">
         <v>196</v>
       </c>
-      <c r="H50" s="118" t="s">
-        <v>272</v>
-      </c>
-      <c r="I50" s="118" t="s">
+      <c r="H50" s="115" t="s">
         <v>271</v>
       </c>
-      <c r="J50" s="33" t="s">
-        <v>272</v>
-      </c>
-      <c r="K50" s="33">
+      <c r="I50" s="115" t="s">
+        <v>270</v>
+      </c>
+      <c r="J50" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="K50" s="30">
         <v>25</v>
       </c>
-      <c r="L50" s="53">
+      <c r="L50" s="50">
         <v>1</v>
       </c>
-      <c r="M50" s="82">
+      <c r="M50" s="79">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N50" s="54" t="s">
+      <c r="N50" s="51" t="s">
         <v>234</v>
       </c>
-      <c r="O50" s="83">
+      <c r="O50" s="80">
         <v>1.1383000000000001</v>
       </c>
-      <c r="P50" s="56">
-        <f>O50*L50</f>
+      <c r="P50" s="53">
+        <f t="shared" si="5"/>
         <v>1.1383000000000001</v>
       </c>
-      <c r="Q50" s="56">
+      <c r="Q50" s="53">
         <v>1.1383000000000001</v>
       </c>
-      <c r="R50" s="56">
-        <f t="shared" si="2"/>
+      <c r="R50" s="53">
+        <f t="shared" si="4"/>
         <v>28.457500000000003</v>
       </c>
-      <c r="S50" s="84"/>
+      <c r="S50" s="81"/>
     </row>
     <row r="51" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="24">
         <v>49</v>
       </c>
-      <c r="B51" s="127" t="s">
+      <c r="B51" s="133" t="s">
         <v>190</v>
       </c>
-      <c r="C51" s="90" t="s">
+      <c r="C51" s="87" t="s">
         <v>59</v>
       </c>
       <c r="D51" s="18" t="s">
         <v>60</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>58</v>
@@ -5168,11 +5176,11 @@
       <c r="H51" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="I51" s="116" t="s">
+      <c r="I51" s="113" t="s">
+        <v>270</v>
+      </c>
+      <c r="J51" s="17" t="s">
         <v>271</v>
-      </c>
-      <c r="J51" s="17" t="s">
-        <v>272</v>
       </c>
       <c r="K51" s="17">
         <v>25</v>
@@ -5191,31 +5199,31 @@
         <v>1.8448</v>
       </c>
       <c r="P51" s="23">
-        <f>O51*L51</f>
+        <f t="shared" si="5"/>
         <v>1.8448</v>
       </c>
       <c r="Q51" s="23">
         <v>1.8448</v>
       </c>
       <c r="R51" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>46.12</v>
       </c>
-      <c r="S51" s="70"/>
+      <c r="S51" s="67"/>
     </row>
-    <row r="52" spans="1:19" s="65" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="124">
+    <row r="52" spans="1:19" s="62" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="119">
         <v>50</v>
       </c>
-      <c r="B52" s="127"/>
-      <c r="C52" s="88" t="s">
+      <c r="B52" s="133"/>
+      <c r="C52" s="85" t="s">
         <v>62</v>
       </c>
       <c r="D52" s="16" t="s">
         <v>63</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>61</v>
@@ -5226,11 +5234,11 @@
       <c r="H52" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="I52" s="125" t="s">
+      <c r="I52" s="120" t="s">
+        <v>270</v>
+      </c>
+      <c r="J52" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="K52" s="2">
         <v>50</v>
@@ -5242,38 +5250,38 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N52" s="63" t="s">
+      <c r="N52" s="60" t="s">
         <v>234</v>
       </c>
       <c r="O52" s="4">
         <v>1.65</v>
       </c>
-      <c r="P52" s="64">
-        <f>O52*L52</f>
+      <c r="P52" s="61">
+        <f t="shared" si="5"/>
         <v>3.3</v>
       </c>
-      <c r="Q52" s="64">
+      <c r="Q52" s="61">
         <v>1.65</v>
       </c>
-      <c r="R52" s="64">
-        <f t="shared" si="2"/>
+      <c r="R52" s="61">
+        <f t="shared" si="4"/>
         <v>82.5</v>
       </c>
-      <c r="S52" s="74"/>
+      <c r="S52" s="71"/>
     </row>
-    <row r="53" spans="1:19" s="65" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="124">
+    <row r="53" spans="1:19" s="62" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="119">
         <v>51</v>
       </c>
-      <c r="B53" s="127"/>
-      <c r="C53" s="88" t="s">
+      <c r="B53" s="133"/>
+      <c r="C53" s="85" t="s">
         <v>65</v>
       </c>
       <c r="D53" s="16" t="s">
         <v>66</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>64</v>
@@ -5294,34 +5302,38 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N53" s="63"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="64">
-        <f>O53*L53</f>
-        <v>0</v>
-      </c>
-      <c r="Q53" s="64"/>
-      <c r="R53" s="64">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S53" s="74" t="s">
-        <v>261</v>
-      </c>
+      <c r="N53" s="60" t="s">
+        <v>338</v>
+      </c>
+      <c r="O53" s="4">
+        <v>1.69</v>
+      </c>
+      <c r="P53" s="61">
+        <f t="shared" si="5"/>
+        <v>1.69</v>
+      </c>
+      <c r="Q53" s="61">
+        <v>1.69</v>
+      </c>
+      <c r="R53" s="61">
+        <f t="shared" si="4"/>
+        <v>1.69</v>
+      </c>
+      <c r="S53" s="71"/>
     </row>
     <row r="54" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="24">
         <v>52</v>
       </c>
-      <c r="B54" s="127"/>
-      <c r="C54" s="87" t="s">
+      <c r="B54" s="133"/>
+      <c r="C54" s="84" t="s">
         <v>68</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>69</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>67</v>
@@ -5329,14 +5341,14 @@
       <c r="G54" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="H54" s="68" t="s">
+      <c r="H54" s="65" t="s">
+        <v>270</v>
+      </c>
+      <c r="I54" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="I54" s="6" t="s">
-        <v>272</v>
-      </c>
       <c r="J54" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K54" s="6">
         <v>30</v>
@@ -5362,24 +5374,24 @@
         <v>0.52100000000000002</v>
       </c>
       <c r="R54" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>15.63</v>
       </c>
-      <c r="S54" s="71"/>
+      <c r="S54" s="68"/>
     </row>
-    <row r="55" spans="1:19" s="65" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="124">
+    <row r="55" spans="1:19" s="62" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="119">
         <v>53</v>
       </c>
-      <c r="B55" s="127"/>
-      <c r="C55" s="88" t="s">
+      <c r="B55" s="133"/>
+      <c r="C55" s="85" t="s">
         <v>81</v>
       </c>
       <c r="D55" s="16" t="s">
         <v>82</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>80</v>
@@ -5387,14 +5399,14 @@
       <c r="G55" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="H55" s="125" t="s">
+      <c r="H55" s="120" t="s">
+        <v>270</v>
+      </c>
+      <c r="I55" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="I55" s="2" t="s">
-        <v>272</v>
-      </c>
       <c r="J55" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K55" s="2">
         <v>50</v>
@@ -5406,31 +5418,31 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="N55" s="63" t="s">
+      <c r="N55" s="60" t="s">
         <v>260</v>
       </c>
       <c r="O55" s="4">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="P55" s="64">
+      <c r="P55" s="61">
         <f>O55*K55</f>
         <v>1.47</v>
       </c>
-      <c r="Q55" s="64">
+      <c r="Q55" s="61">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="R55" s="64">
-        <f t="shared" si="2"/>
+      <c r="R55" s="61">
+        <f t="shared" si="4"/>
         <v>1.47</v>
       </c>
-      <c r="S55" s="74"/>
+      <c r="S55" s="71"/>
     </row>
     <row r="56" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="24">
         <v>54</v>
       </c>
-      <c r="B56" s="127"/>
-      <c r="C56" s="87" t="s">
+      <c r="B56" s="133"/>
+      <c r="C56" s="84" t="s">
         <v>86</v>
       </c>
       <c r="D56" s="14" t="s">
@@ -5440,19 +5452,19 @@
         <v>88</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="H56" s="68" t="s">
+      <c r="H56" s="65" t="s">
+        <v>270</v>
+      </c>
+      <c r="I56" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="I56" s="6" t="s">
-        <v>272</v>
-      </c>
       <c r="J56" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K56" s="6">
         <v>50</v>
@@ -5478,17 +5490,17 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="R56" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4500000000000002</v>
       </c>
-      <c r="S56" s="93"/>
+      <c r="S56" s="90"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="24">
         <v>55</v>
       </c>
-      <c r="B57" s="127"/>
-      <c r="C57" s="91" t="s">
+      <c r="B57" s="133"/>
+      <c r="C57" s="88" t="s">
         <v>83</v>
       </c>
       <c r="D57" s="12" t="s">
@@ -5500,18 +5512,18 @@
       <c r="F57" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="G57" s="69" t="s">
-        <v>271</v>
-      </c>
-      <c r="H57" s="69" t="s">
-        <v>271</v>
-      </c>
-      <c r="I57" s="69" t="s">
-        <v>271</v>
+      <c r="G57" s="66" t="s">
+        <v>270</v>
+      </c>
+      <c r="H57" s="66" t="s">
+        <v>270</v>
+      </c>
+      <c r="I57" s="66" t="s">
+        <v>270</v>
       </c>
       <c r="J57" s="12"/>
       <c r="K57" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L57" s="13">
         <v>4</v>
@@ -5520,79 +5532,79 @@
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="N57" s="69" t="s">
-        <v>271</v>
-      </c>
-      <c r="O57" s="69" t="s">
-        <v>271</v>
-      </c>
-      <c r="P57" s="69" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q57" s="69" t="s">
-        <v>271</v>
-      </c>
-      <c r="R57" s="69" t="s">
-        <v>271</v>
-      </c>
-      <c r="S57" s="75" t="s">
-        <v>333</v>
+      <c r="N57" s="66" t="s">
+        <v>270</v>
+      </c>
+      <c r="O57" s="66" t="s">
+        <v>270</v>
+      </c>
+      <c r="P57" s="66" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q57" s="66" t="s">
+        <v>270</v>
+      </c>
+      <c r="R57" s="66" t="s">
+        <v>270</v>
+      </c>
+      <c r="S57" s="72" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="58" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="24">
         <v>56</v>
       </c>
-      <c r="B58" s="128"/>
-      <c r="C58" s="94" t="s">
+      <c r="B58" s="134"/>
+      <c r="C58" s="91" t="s">
         <v>143</v>
       </c>
-      <c r="D58" s="76" t="s">
-        <v>332</v>
-      </c>
-      <c r="E58" s="76" t="s">
+      <c r="D58" s="73" t="s">
+        <v>331</v>
+      </c>
+      <c r="E58" s="73" t="s">
         <v>142</v>
       </c>
-      <c r="F58" s="76" t="s">
+      <c r="F58" s="73" t="s">
         <v>142</v>
       </c>
-      <c r="G58" s="77" t="s">
-        <v>271</v>
-      </c>
-      <c r="H58" s="77" t="s">
-        <v>271</v>
-      </c>
-      <c r="I58" s="77" t="s">
-        <v>271</v>
-      </c>
-      <c r="J58" s="76"/>
-      <c r="K58" s="76" t="s">
-        <v>334</v>
-      </c>
-      <c r="L58" s="78">
+      <c r="G58" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="H58" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="I58" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="J58" s="73"/>
+      <c r="K58" s="73" t="s">
+        <v>333</v>
+      </c>
+      <c r="L58" s="75">
         <v>1</v>
       </c>
-      <c r="M58" s="82">
+      <c r="M58" s="79">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N58" s="77" t="s">
-        <v>271</v>
-      </c>
-      <c r="O58" s="77" t="s">
-        <v>271</v>
-      </c>
-      <c r="P58" s="77" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q58" s="77" t="s">
-        <v>271</v>
-      </c>
-      <c r="R58" s="77" t="s">
-        <v>271</v>
-      </c>
-      <c r="S58" s="79" t="s">
-        <v>333</v>
+      <c r="N58" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="O58" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="P58" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q58" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="R58" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="S58" s="76" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="59" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -5605,31 +5617,31 @@
       <c r="I59" s="10"/>
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
-      <c r="L59" s="119" t="s">
-        <v>337</v>
-      </c>
-      <c r="M59" s="119"/>
-      <c r="N59" s="119"/>
-      <c r="O59" s="119"/>
-      <c r="R59" s="120">
+      <c r="L59" s="127" t="s">
+        <v>336</v>
+      </c>
+      <c r="M59" s="127"/>
+      <c r="N59" s="127"/>
+      <c r="O59" s="127"/>
+      <c r="R59" s="116">
         <f>SUM(R3:R58)</f>
-        <v>695.55850000000021</v>
+        <v>697.24850000000026</v>
       </c>
     </row>
     <row r="60" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="L60" s="121" t="s">
-        <v>338</v>
-      </c>
-      <c r="M60" s="121"/>
-      <c r="N60" s="121"/>
-      <c r="O60" s="121"/>
-      <c r="P60" s="122">
+      <c r="L60" s="128" t="s">
+        <v>337</v>
+      </c>
+      <c r="M60" s="128"/>
+      <c r="N60" s="128"/>
+      <c r="O60" s="128"/>
+      <c r="P60" s="117">
         <f>SUM(P3:P59)</f>
-        <v>92.029800000000009</v>
-      </c>
-      <c r="R60" s="123">
+        <v>93.719800000000006</v>
+      </c>
+      <c r="R60" s="118">
         <f>R59/25</f>
-        <v>27.822340000000008</v>
+        <v>27.88994000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5925,59 +5937,59 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N3" r:id="rId1"/>
-    <hyperlink ref="N4" r:id="rId2"/>
-    <hyperlink ref="N5" r:id="rId3"/>
-    <hyperlink ref="N6" r:id="rId4"/>
-    <hyperlink ref="N7" r:id="rId5"/>
-    <hyperlink ref="N8" r:id="rId6"/>
-    <hyperlink ref="N9" r:id="rId7"/>
-    <hyperlink ref="N12" r:id="rId8"/>
-    <hyperlink ref="N13" r:id="rId9"/>
-    <hyperlink ref="N15" r:id="rId10"/>
-    <hyperlink ref="N16" r:id="rId11"/>
-    <hyperlink ref="N18" r:id="rId12"/>
-    <hyperlink ref="N19" r:id="rId13"/>
-    <hyperlink ref="N21" r:id="rId14"/>
-    <hyperlink ref="N22" r:id="rId15"/>
-    <hyperlink ref="N23" r:id="rId16"/>
-    <hyperlink ref="N24" r:id="rId17"/>
-    <hyperlink ref="N25" r:id="rId18"/>
-    <hyperlink ref="N26" r:id="rId19"/>
-    <hyperlink ref="N43" r:id="rId20"/>
-    <hyperlink ref="N44" r:id="rId21"/>
-    <hyperlink ref="N45" r:id="rId22"/>
-    <hyperlink ref="N50" r:id="rId23"/>
-    <hyperlink ref="N51" r:id="rId24"/>
-    <hyperlink ref="N55" r:id="rId25" display="LCSC"/>
-    <hyperlink ref="N49" r:id="rId26"/>
-    <hyperlink ref="N54" r:id="rId27"/>
-    <hyperlink ref="N42" r:id="rId28"/>
-    <hyperlink ref="N17" r:id="rId29"/>
-    <hyperlink ref="N10" r:id="rId30"/>
-    <hyperlink ref="N11" r:id="rId31"/>
-    <hyperlink ref="N14" r:id="rId32"/>
-    <hyperlink ref="N20" r:id="rId33"/>
-    <hyperlink ref="N27" r:id="rId34"/>
-    <hyperlink ref="N28" r:id="rId35"/>
-    <hyperlink ref="N29" r:id="rId36"/>
-    <hyperlink ref="N30" r:id="rId37"/>
-    <hyperlink ref="N31" r:id="rId38"/>
-    <hyperlink ref="N33" r:id="rId39"/>
-    <hyperlink ref="N34" r:id="rId40"/>
-    <hyperlink ref="N35" r:id="rId41"/>
-    <hyperlink ref="N37" r:id="rId42"/>
-    <hyperlink ref="N39" r:id="rId43"/>
-    <hyperlink ref="N40" r:id="rId44"/>
-    <hyperlink ref="N41" r:id="rId45"/>
-    <hyperlink ref="N46" r:id="rId46"/>
-    <hyperlink ref="N47" r:id="rId47"/>
-    <hyperlink ref="N48" r:id="rId48"/>
-    <hyperlink ref="N52" r:id="rId49"/>
-    <hyperlink ref="N56" r:id="rId50"/>
-    <hyperlink ref="N32" r:id="rId51"/>
-    <hyperlink ref="N36" r:id="rId52"/>
-    <hyperlink ref="N38" r:id="rId53"/>
+    <hyperlink ref="N3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N9" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N12" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N13" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N15" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N16" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N18" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N19" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N21" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N22" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N23" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N24" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N25" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N26" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N43" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N44" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N45" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N50" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N51" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N55" r:id="rId25" display="LCSC" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N49" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N54" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N42" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N17" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="N10" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N11" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="N14" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N20" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N27" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N28" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="N29" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="N30" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N31" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="N33" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N34" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="N35" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="N37" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="N39" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="N40" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="N41" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="N46" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N47" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="N48" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="N52" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="N56" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="N32" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="N36" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="N38" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId54"/>
